--- a/docs/verbali/FloreMoria_2026_T3_Corrispettivi.xlsx
+++ b/docs/verbali/FloreMoria_2026_T3_Corrispettivi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="95">
   <si>
     <t>Ragione sociale</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Data e ora generazione</t>
   </si>
   <si>
-    <t>20/09/2026, 19:23:47</t>
+    <t>21/09/2026, 22:23:50</t>
   </si>
   <si>
     <t>Voce</t>
@@ -80,13 +80,7 @@
     <t>Nota 3</t>
   </si>
   <si>
-    <t>Foglio F3 (costi fiorista senza documento) sospeso: rientrerà quando l’abbinamento bonifici→consegne sarà corretto. Non usare i movimenti bancari come proxy del costo per consegna.</t>
-  </si>
-  <si>
-    <t>Nota 4</t>
-  </si>
-  <si>
-    <t>Prima di chiudere il trimestre caricare l’estratto conto Fineco aggiornato in Contabilità → Movimenti bancari.</t>
+    <t>I costi verso i fioristi sono comunicati separatamente.</t>
   </si>
   <si>
     <t>Data ordine</t>
@@ -101,85 +95,216 @@
     <t>IVA EUR</t>
   </si>
   <si>
+    <t>02/07/2026</t>
+  </si>
+  <si>
     <t>eu-2026-035</t>
   </si>
   <si>
     <t>Stripe</t>
   </si>
   <si>
+    <t>03/07/2026</t>
+  </si>
+  <si>
     <t>eu-2026-036</t>
   </si>
   <si>
-    <t>DA_COLLEGARE</t>
+    <t>04/07/2026</t>
+  </si>
+  <si>
+    <t>py_3TpOrX4W4pZWhSUs0bWli3kl</t>
+  </si>
+  <si>
+    <t>PayPal (via Stripe)</t>
+  </si>
+  <si>
+    <t>py_3TpPFc4W4pZWhSUs0s0z7zvu</t>
+  </si>
+  <si>
+    <t>py_3TpPJU4W4pZWhSUs1N3Am5Ht</t>
+  </si>
+  <si>
+    <t>09/07/2026</t>
   </si>
   <si>
     <t>eu-2026-037</t>
   </si>
   <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>6TL5310123588930U</t>
+  </si>
+  <si>
     <t>PayPal</t>
   </si>
   <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
     <t>eu-2026-038</t>
   </si>
   <si>
+    <t>19/07/2026</t>
+  </si>
+  <si>
     <t>FT-MB-26-001</t>
   </si>
   <si>
+    <t>30/07/2026</t>
+  </si>
+  <si>
+    <t>py_3TyuIF4W4pZWhSUs01ynUG53</t>
+  </si>
+  <si>
+    <t>py_3TyuTV4W4pZWhSUs00PZNqwe</t>
+  </si>
+  <si>
+    <t>01/08/2026</t>
+  </si>
+  <si>
     <t>eu-2026-039</t>
   </si>
   <si>
+    <t>04/08/2026</t>
+  </si>
+  <si>
+    <t>ch_3U0cT94W4pZWhSUs0zCmlTCo</t>
+  </si>
+  <si>
+    <t>06/08/2026</t>
+  </si>
+  <si>
     <t>eu-2026-040</t>
   </si>
   <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
     <t>eu-2026-041</t>
   </si>
   <si>
+    <t>13/08/2026</t>
+  </si>
+  <si>
+    <t>py_3U44XP4W4pZWhSUs0AsseGiK</t>
+  </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>py_3U5QyD4W4pZWhSUs1Lgk1VNp</t>
+  </si>
+  <si>
+    <t>py_3U5R2d4W4pZWhSUs0IA5ZBux</t>
+  </si>
+  <si>
     <t>eu-2026-042</t>
   </si>
   <si>
+    <t>19/08/2026</t>
+  </si>
+  <si>
     <t>FT-RC-26-003</t>
   </si>
   <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
     <t>eu-2026-043</t>
   </si>
   <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
     <t>FT-LC-26-001</t>
   </si>
   <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
     <t>FF-VI-26-003</t>
   </si>
   <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
     <t>FT-TO-26-001</t>
   </si>
   <si>
     <t>FT-TO-26-002</t>
   </si>
   <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
     <t>FF-SO-26-001</t>
   </si>
   <si>
+    <t>01/09/2026</t>
+  </si>
+  <si>
     <t>FT-CS-26-007</t>
   </si>
   <si>
     <t>FT-PA-26-009</t>
   </si>
   <si>
+    <t>05/09/2026</t>
+  </si>
+  <si>
     <t>FF-MC-26-001</t>
   </si>
   <si>
     <t>FF-MC-26-002</t>
   </si>
   <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>22A12950PA842023C</t>
+  </si>
+  <si>
+    <t>12/09/2026</t>
+  </si>
+  <si>
     <t>FT-ME-26-003</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>ch_3UFsdS4W4pZWhSUs1jZEbaY6</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>ch_3UGKB9RrkwwcYwep0iX4YzwT</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>ch_3UGhhKRrkwwcYwep0oDybDle</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>FT-PA-26-010</t>
+  </si>
+  <si>
+    <t>FT-CS-26-008</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="€ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -245,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -255,7 +380,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -663,19 +787,19 @@
         <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3">
-        <v>1902.66</v>
+        <v>1959.9</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
       </c>
       <c r="E7" s="3">
-        <v>190.25</v>
+        <v>195.97</v>
       </c>
       <c r="F7" s="3">
-        <v>2092.91</v>
+        <v>2155.87</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -683,19 +807,19 @@
         <v>15</v>
       </c>
       <c r="B8" s="5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="6">
-        <v>1902.66</v>
+        <v>1959.9</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="6">
-        <v>190.25</v>
+        <v>195.97</v>
       </c>
       <c r="F8" s="6">
-        <v>2092.91</v>
+        <v>2155.87</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25"/>
@@ -721,14 +845,6 @@
       </c>
       <c r="B12" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -739,12 +855,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
@@ -752,13 +868,13 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -767,21 +883,21 @@
         <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>46205.41666666667</v>
+      <c r="A2" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
         <v>95.44</v>
@@ -797,14 +913,14 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>46206.41666666667</v>
+      <c r="A3" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3">
         <v>63.63</v>
@@ -820,14 +936,14 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>46207.41666666667</v>
+      <c r="A4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3">
         <v>131.8</v>
@@ -843,14 +959,14 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>46207.41666666667</v>
+      <c r="A5" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3">
         <v>28.62</v>
@@ -866,14 +982,14 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>46207.41666666667</v>
+      <c r="A6" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3">
         <v>28.62</v>
@@ -889,14 +1005,14 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>46212.41666666667</v>
+      <c r="A7" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3">
         <v>36.35</v>
@@ -912,14 +1028,14 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>46218.41666666667</v>
+      <c r="A8" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D8" s="3">
         <v>45.45</v>
@@ -935,14 +1051,14 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>46219.41666666667</v>
+      <c r="A9" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3">
         <v>34.54</v>
@@ -958,14 +1074,14 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>46222.41666666667</v>
+      <c r="A10" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3">
         <v>34.54</v>
@@ -981,14 +1097,14 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>46233.41666666667</v>
+      <c r="A11" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3">
         <v>28.62</v>
@@ -1004,14 +1120,14 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>46233.41666666667</v>
+      <c r="A12" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3">
         <v>28.62</v>
@@ -1027,14 +1143,14 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>46235.41666666667</v>
+      <c r="A13" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3">
         <v>27.26</v>
@@ -1050,14 +1166,14 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>46238.41666666667</v>
+      <c r="A14" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3">
         <v>43.15</v>
@@ -1073,14 +1189,14 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>46240.41666666667</v>
+      <c r="A15" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="3">
         <v>36.35</v>
@@ -1096,14 +1212,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>46244.41666666667</v>
+      <c r="A16" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="3">
         <v>63.63</v>
@@ -1119,14 +1235,14 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>46247.41666666667</v>
+      <c r="A17" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="3">
         <v>47.71</v>
@@ -1142,14 +1258,14 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>46251.41666666667</v>
+      <c r="A18" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D18" s="3">
         <v>28.62</v>
@@ -1165,14 +1281,14 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>46251.41666666667</v>
+      <c r="A19" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D19" s="3">
         <v>28.62</v>
@@ -1188,14 +1304,14 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>46251.41666666667</v>
+      <c r="A20" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3">
         <v>36.35</v>
@@ -1211,14 +1327,14 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>46253.41666666667</v>
+      <c r="A21" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3">
         <v>43.15</v>
@@ -1234,14 +1350,14 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>46255.41666666667</v>
+      <c r="A22" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3">
         <v>81.81</v>
@@ -1257,14 +1373,14 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>46258.41666666667</v>
+      <c r="A23" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D23" s="3">
         <v>49.06</v>
@@ -1280,14 +1396,14 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>46260.41666666667</v>
+      <c r="A24" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3">
         <v>48.16</v>
@@ -1303,14 +1419,14 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>46262.41666666667</v>
+      <c r="A25" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="3">
         <v>27.26</v>
@@ -1326,14 +1442,14 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>46262.41666666667</v>
+      <c r="A26" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="3">
         <v>27.26</v>
@@ -1349,14 +1465,14 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>46265.41666666667</v>
+      <c r="A27" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="3">
         <v>77.25</v>
@@ -1372,14 +1488,14 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>46266.41666666667</v>
+      <c r="A28" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D28" s="3">
         <v>28.62</v>
@@ -1395,14 +1511,14 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>46266.41666666667</v>
+      <c r="A29" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D29" s="3">
         <v>28.62</v>
@@ -1418,14 +1534,14 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>46270.41666666667</v>
+      <c r="A30" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="3">
         <v>95.44</v>
@@ -1441,14 +1557,14 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>46270.41666666667</v>
+      <c r="A31" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="3">
         <v>186.35</v>
@@ -1464,14 +1580,14 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>46274.41666666667</v>
+      <c r="A32" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D32" s="3">
         <v>50.9</v>
@@ -1487,14 +1603,14 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>46277.41666666667</v>
+      <c r="A33" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D33" s="3">
         <v>45.45</v>
@@ -1510,14 +1626,14 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>46280.41666666667</v>
+      <c r="A34" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="3">
         <v>27.26</v>
@@ -1533,14 +1649,14 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>46281.41666666667</v>
+      <c r="A35" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" s="3">
         <v>118.17</v>
@@ -1556,14 +1672,14 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>46282.41666666667</v>
+      <c r="A36" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="3">
         <v>99.98</v>
@@ -1578,27 +1694,73 @@
         <v>109.98</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="3">
+        <v>28.62</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2.86</v>
+      </c>
+      <c r="G37" s="3">
+        <v>31.48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="3">
+        <v>28.62</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2.86</v>
+      </c>
+      <c r="G38" s="3">
+        <v>31.48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="6">
-        <v>1902.66</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="D39" s="6">
+        <v>1959.9</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F37" s="6">
-        <v>190.25</v>
-      </c>
-      <c r="G37" s="6">
-        <v>2092.91</v>
+      <c r="F39" s="6">
+        <v>195.97</v>
+      </c>
+      <c r="G39" s="6">
+        <v>2155.87</v>
       </c>
     </row>
   </sheetData>
